--- a/app/配件表模板.xlsx
+++ b/app/配件表模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\yonyou\TidanMgr-R1\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDFB301-E78D-4B4A-BDD0-2275BB3AC7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A0377C-D708-4266-8164-EE1E3A18FE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="已拆包平台" sheetId="4" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">配件表!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">已拆包平台!$A$1:$D$422</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="767">
   <si>
     <t>任务名</t>
   </si>
@@ -2429,13 +2430,7 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>APP</t>
-  </si>
-  <si>
     <t>小程序</t>
-  </si>
-  <si>
-    <t>公众号</t>
   </si>
   <si>
     <t>名称A</t>
@@ -3133,7 +3128,7 @@
         <v>725</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>726</v>
@@ -3145,7 +3140,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
@@ -3156,16 +3151,16 @@
         <v>728</v>
       </c>
       <c r="C2" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>734</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>736</v>
-      </c>
       <c r="E2" s="31" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -3182,16 +3177,16 @@
         <v>728</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -3208,16 +3203,16 @@
         <v>728</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -3234,16 +3229,16 @@
         <v>728</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -3254,22 +3249,22 @@
     </row>
     <row r="6" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>728</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3280,22 +3275,22 @@
     </row>
     <row r="7" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>728</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3306,22 +3301,22 @@
     </row>
     <row r="8" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>728</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -3338,16 +3333,16 @@
         <v>729</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -3364,16 +3359,16 @@
         <v>729</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3390,16 +3385,16 @@
         <v>729</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -3416,16 +3411,16 @@
         <v>729</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -3436,22 +3431,22 @@
     </row>
     <row r="13" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>729</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -3462,22 +3457,22 @@
     </row>
     <row r="14" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>730</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -3488,22 +3483,22 @@
     </row>
     <row r="15" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>730</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -3513,7 +3508,9 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A16" s="12"/>
+      <c r="A16" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B16" s="26"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -3527,7 +3524,9 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A17" s="12"/>
+      <c r="A17" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B17" s="26"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -3541,7 +3540,9 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A18" s="12"/>
+      <c r="A18" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B18" s="26"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -3555,7 +3556,9 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A19" s="12"/>
+      <c r="A19" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B19" s="26"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -3569,7 +3572,9 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A20" s="12"/>
+      <c r="A20" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B20" s="26"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -3583,7 +3588,9 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A21" s="12"/>
+      <c r="A21" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B21" s="26"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -3597,7 +3604,9 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A22" s="12"/>
+      <c r="A22" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B22" s="26"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -3611,7 +3620,9 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A23" s="12"/>
+      <c r="A23" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B23" s="26"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -3625,7 +3636,9 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A24" s="12"/>
+      <c r="A24" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B24" s="26"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -3639,7 +3652,9 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A25" s="12"/>
+      <c r="A25" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B25" s="26"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -3653,7 +3668,9 @@
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A26" s="12"/>
+      <c r="A26" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B26" s="26"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -3667,7 +3684,9 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A27" s="12"/>
+      <c r="A27" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B27" s="26"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -3681,7 +3700,9 @@
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A28" s="12"/>
+      <c r="A28" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B28" s="26"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -3695,7 +3716,9 @@
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A29" s="12"/>
+      <c r="A29" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B29" s="26"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -3709,7 +3732,9 @@
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A30" s="12"/>
+      <c r="A30" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B30" s="11"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -3723,7 +3748,9 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A31" s="12"/>
+      <c r="A31" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B31" s="11"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
@@ -3737,7 +3764,9 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A32" s="12"/>
+      <c r="A32" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -3751,7 +3780,9 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A33" s="12"/>
+      <c r="A33" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B33" s="16"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -3765,7 +3796,9 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A34" s="12"/>
+      <c r="A34" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B34" s="11"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -3779,7 +3812,9 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A35" s="12"/>
+      <c r="A35" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B35" s="11"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -3793,7 +3828,9 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A36" s="12"/>
+      <c r="A36" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B36" s="18"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -3807,7 +3844,9 @@
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A37" s="12"/>
+      <c r="A37" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B37" s="20"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -3821,7 +3860,9 @@
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A38" s="12"/>
+      <c r="A38" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B38" s="18"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3835,7 +3876,9 @@
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A39" s="12"/>
+      <c r="A39" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B39" s="16"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
@@ -3849,7 +3892,9 @@
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A40" s="12"/>
+      <c r="A40" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B40" s="11"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -3863,7 +3908,9 @@
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A41" s="12"/>
+      <c r="A41" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B41" s="11"/>
       <c r="C41" s="13"/>
       <c r="D41" s="13"/>
@@ -3877,7 +3924,9 @@
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A42" s="12"/>
+      <c r="A42" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B42" s="18"/>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -3891,7 +3940,9 @@
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A43" s="12"/>
+      <c r="A43" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B43" s="16"/>
       <c r="C43" s="13"/>
       <c r="D43" s="13"/>
@@ -3905,7 +3956,9 @@
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A44" s="12"/>
+      <c r="A44" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B44" s="11"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -3919,7 +3972,9 @@
       <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A45" s="12"/>
+      <c r="A45" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B45" s="11"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -3933,7 +3988,9 @@
       <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A46" s="12"/>
+      <c r="A46" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B46" s="18"/>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -3947,7 +4004,9 @@
       <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A47" s="12"/>
+      <c r="A47" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B47" s="20"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3961,7 +4020,9 @@
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A48" s="12"/>
+      <c r="A48" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B48" s="18"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3975,7 +4036,9 @@
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A49" s="12"/>
+      <c r="A49" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B49" s="16"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3989,7 +4052,9 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A50" s="12"/>
+      <c r="A50" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B50" s="11"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -4003,7 +4068,9 @@
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A51" s="12"/>
+      <c r="A51" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B51" s="11"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -4017,7 +4084,9 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A52" s="12"/>
+      <c r="A52" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B52" s="18"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -4031,7 +4100,9 @@
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A53" s="12"/>
+      <c r="A53" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B53" s="16"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -4045,7 +4116,9 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A54" s="12"/>
+      <c r="A54" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B54" s="11"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -4059,7 +4132,9 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A55" s="12"/>
+      <c r="A55" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B55" s="11"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -4073,7 +4148,9 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A56" s="12"/>
+      <c r="A56" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B56" s="18"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -4087,7 +4164,9 @@
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A57" s="12"/>
+      <c r="A57" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B57" s="20"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
@@ -4101,7 +4180,9 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A58" s="12"/>
+      <c r="A58" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B58" s="18"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -4115,7 +4196,9 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A59" s="12"/>
+      <c r="A59" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B59" s="16"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -4129,7 +4212,9 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A60" s="12"/>
+      <c r="A60" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B60" s="11"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -4143,7 +4228,9 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A61" s="12"/>
+      <c r="A61" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B61" s="11"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -4157,7 +4244,9 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A62" s="12"/>
+      <c r="A62" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B62" s="18"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
@@ -4171,7 +4260,9 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A63" s="12"/>
+      <c r="A63" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B63" s="16"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -4185,7 +4276,9 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A64" s="12"/>
+      <c r="A64" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B64" s="11"/>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -4199,7 +4292,9 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A65" s="12"/>
+      <c r="A65" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B65" s="11"/>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -4213,7 +4308,9 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A66" s="12"/>
+      <c r="A66" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B66" s="18"/>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>
@@ -4227,7 +4324,9 @@
       <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A67" s="12"/>
+      <c r="A67" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B67" s="20"/>
       <c r="C67" s="13"/>
       <c r="D67" s="13"/>
@@ -4241,7 +4340,9 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A68" s="12"/>
+      <c r="A68" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B68" s="18"/>
       <c r="C68" s="13"/>
       <c r="D68" s="13"/>
@@ -4255,7 +4356,9 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A69" s="12"/>
+      <c r="A69" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B69" s="20"/>
       <c r="C69" s="13"/>
       <c r="D69" s="13"/>
@@ -4269,7 +4372,9 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A70" s="12"/>
+      <c r="A70" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B70" s="18"/>
       <c r="C70" s="13"/>
       <c r="D70" s="13"/>
@@ -4283,7 +4388,9 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A71" s="12"/>
+      <c r="A71" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B71" s="16"/>
       <c r="C71" s="13"/>
       <c r="D71" s="13"/>
@@ -4297,7 +4404,9 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A72" s="12"/>
+      <c r="A72" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B72" s="11"/>
       <c r="C72" s="13"/>
       <c r="D72" s="13"/>
@@ -4311,7 +4420,9 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A73" s="12"/>
+      <c r="A73" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B73" s="16"/>
       <c r="C73" s="13"/>
       <c r="D73" s="13"/>
@@ -4325,7 +4436,9 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A74" s="12"/>
+      <c r="A74" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B74" s="11"/>
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
@@ -4339,7 +4452,9 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A75" s="12"/>
+      <c r="A75" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B75" s="11"/>
       <c r="C75" s="13"/>
       <c r="D75" s="13"/>
@@ -4353,7 +4468,9 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A76" s="12"/>
+      <c r="A76" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B76" s="18"/>
       <c r="C76" s="13"/>
       <c r="D76" s="13"/>
@@ -4367,7 +4484,9 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A77" s="12"/>
+      <c r="A77" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B77" s="16"/>
       <c r="C77" s="13"/>
       <c r="D77" s="13"/>
@@ -4381,7 +4500,9 @@
       <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A78" s="12"/>
+      <c r="A78" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B78" s="11"/>
       <c r="C78" s="13"/>
       <c r="D78" s="13"/>
@@ -4395,7 +4516,9 @@
       <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A79" s="12"/>
+      <c r="A79" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B79" s="11"/>
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
@@ -4409,7 +4532,9 @@
       <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A80" s="12"/>
+      <c r="A80" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B80" s="18"/>
       <c r="C80" s="13"/>
       <c r="D80" s="13"/>
@@ -4423,7 +4548,9 @@
       <c r="L80" s="2"/>
     </row>
     <row r="81" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A81" s="12"/>
+      <c r="A81" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B81" s="20"/>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -4437,7 +4564,9 @@
       <c r="L81" s="2"/>
     </row>
     <row r="82" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A82" s="12"/>
+      <c r="A82" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B82" s="18"/>
       <c r="C82" s="13"/>
       <c r="D82" s="13"/>
@@ -4451,7 +4580,9 @@
       <c r="L82" s="2"/>
     </row>
     <row r="83" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A83" s="12"/>
+      <c r="A83" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B83" s="16"/>
       <c r="C83" s="13"/>
       <c r="D83" s="13"/>
@@ -4465,7 +4596,9 @@
       <c r="L83" s="2"/>
     </row>
     <row r="84" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A84" s="12"/>
+      <c r="A84" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B84" s="11"/>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
@@ -4479,7 +4612,9 @@
       <c r="L84" s="2"/>
     </row>
     <row r="85" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A85" s="12"/>
+      <c r="A85" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B85" s="11"/>
       <c r="C85" s="13"/>
       <c r="D85" s="13"/>
@@ -4493,7 +4628,9 @@
       <c r="L85" s="2"/>
     </row>
     <row r="86" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A86" s="12"/>
+      <c r="A86" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B86" s="18"/>
       <c r="C86" s="13"/>
       <c r="D86" s="13"/>
@@ -4507,7 +4644,9 @@
       <c r="L86" s="2"/>
     </row>
     <row r="87" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A87" s="12"/>
+      <c r="A87" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B87" s="16"/>
       <c r="C87" s="13"/>
       <c r="D87" s="13"/>
@@ -4521,7 +4660,9 @@
       <c r="L87" s="2"/>
     </row>
     <row r="88" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A88" s="12"/>
+      <c r="A88" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B88" s="11"/>
       <c r="C88" s="13"/>
       <c r="D88" s="13"/>
@@ -4535,7 +4676,9 @@
       <c r="L88" s="2"/>
     </row>
     <row r="89" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A89" s="12"/>
+      <c r="A89" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B89" s="11"/>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
@@ -4549,7 +4692,9 @@
       <c r="L89" s="2"/>
     </row>
     <row r="90" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A90" s="12"/>
+      <c r="A90" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B90" s="18"/>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
@@ -4563,7 +4708,9 @@
       <c r="L90" s="2"/>
     </row>
     <row r="91" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A91" s="12"/>
+      <c r="A91" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B91" s="20"/>
       <c r="C91" s="13"/>
       <c r="D91" s="13"/>
@@ -4577,7 +4724,9 @@
       <c r="L91" s="2"/>
     </row>
     <row r="92" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A92" s="12"/>
+      <c r="A92" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B92" s="18"/>
       <c r="C92" s="13"/>
       <c r="D92" s="13"/>
@@ -4591,7 +4740,9 @@
       <c r="L92" s="2"/>
     </row>
     <row r="93" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A93" s="12"/>
+      <c r="A93" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B93" s="16"/>
       <c r="C93" s="13"/>
       <c r="D93" s="13"/>
@@ -4605,7 +4756,9 @@
       <c r="L93" s="2"/>
     </row>
     <row r="94" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A94" s="12"/>
+      <c r="A94" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B94" s="11"/>
       <c r="C94" s="13"/>
       <c r="D94" s="13"/>
@@ -4619,7 +4772,9 @@
       <c r="L94" s="2"/>
     </row>
     <row r="95" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A95" s="12"/>
+      <c r="A95" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B95" s="11"/>
       <c r="C95" s="13"/>
       <c r="D95" s="13"/>
@@ -4633,7 +4788,9 @@
       <c r="L95" s="2"/>
     </row>
     <row r="96" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A96" s="12"/>
+      <c r="A96" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B96" s="18"/>
       <c r="C96" s="13"/>
       <c r="D96" s="13"/>
@@ -4647,7 +4804,9 @@
       <c r="L96" s="2"/>
     </row>
     <row r="97" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A97" s="12"/>
+      <c r="A97" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B97" s="16"/>
       <c r="C97" s="13"/>
       <c r="D97" s="13"/>
@@ -4661,7 +4820,9 @@
       <c r="L97" s="2"/>
     </row>
     <row r="98" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A98" s="12"/>
+      <c r="A98" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B98" s="11"/>
       <c r="C98" s="13"/>
       <c r="D98" s="13"/>
@@ -4675,7 +4836,9 @@
       <c r="L98" s="2"/>
     </row>
     <row r="99" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A99" s="12"/>
+      <c r="A99" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B99" s="11"/>
       <c r="C99" s="13"/>
       <c r="D99" s="13"/>
@@ -4689,7 +4852,9 @@
       <c r="L99" s="2"/>
     </row>
     <row r="100" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A100" s="12"/>
+      <c r="A100" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B100" s="18"/>
       <c r="C100" s="13"/>
       <c r="D100" s="13"/>
@@ -4703,7 +4868,9 @@
       <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A101" s="12"/>
+      <c r="A101" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B101" s="20"/>
       <c r="C101" s="13"/>
       <c r="D101" s="13"/>
@@ -4717,7 +4884,9 @@
       <c r="L101" s="2"/>
     </row>
     <row r="102" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A102" s="12"/>
+      <c r="A102" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B102" s="18"/>
       <c r="C102" s="13"/>
       <c r="D102" s="13"/>
@@ -4731,7 +4900,9 @@
       <c r="L102" s="2"/>
     </row>
     <row r="103" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A103" s="12"/>
+      <c r="A103" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B103" s="16"/>
       <c r="C103" s="13"/>
       <c r="D103" s="13"/>
@@ -4745,7 +4916,9 @@
       <c r="L103" s="2"/>
     </row>
     <row r="104" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A104" s="12"/>
+      <c r="A104" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B104" s="11"/>
       <c r="C104" s="13"/>
       <c r="D104" s="13"/>
@@ -4759,7 +4932,9 @@
       <c r="L104" s="2"/>
     </row>
     <row r="105" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A105" s="12"/>
+      <c r="A105" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B105" s="11"/>
       <c r="C105" s="13"/>
       <c r="D105" s="13"/>
@@ -4773,7 +4948,9 @@
       <c r="L105" s="2"/>
     </row>
     <row r="106" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A106" s="12"/>
+      <c r="A106" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B106" s="18"/>
       <c r="C106" s="13"/>
       <c r="D106" s="13"/>
@@ -4787,7 +4964,9 @@
       <c r="L106" s="2"/>
     </row>
     <row r="107" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A107" s="12"/>
+      <c r="A107" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B107" s="16"/>
       <c r="C107" s="13"/>
       <c r="D107" s="13"/>
@@ -4801,7 +4980,9 @@
       <c r="L107" s="2"/>
     </row>
     <row r="108" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A108" s="12"/>
+      <c r="A108" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B108" s="11"/>
       <c r="C108" s="12"/>
       <c r="D108" s="13"/>
@@ -4815,7 +4996,9 @@
       <c r="L108" s="2"/>
     </row>
     <row r="109" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A109" s="12"/>
+      <c r="A109" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B109" s="11"/>
       <c r="C109" s="12"/>
       <c r="D109" s="13"/>
@@ -4829,7 +5012,9 @@
       <c r="L109" s="2"/>
     </row>
     <row r="110" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A110" s="12"/>
+      <c r="A110" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B110" s="18"/>
       <c r="C110" s="12"/>
       <c r="D110" s="13"/>
@@ -4843,7 +5028,9 @@
       <c r="L110" s="2"/>
     </row>
     <row r="111" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A111" s="12"/>
+      <c r="A111" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B111" s="20"/>
       <c r="C111" s="13"/>
       <c r="D111" s="13"/>
@@ -4857,7 +5044,9 @@
       <c r="L111" s="2"/>
     </row>
     <row r="112" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A112" s="12"/>
+      <c r="A112" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B112" s="18"/>
       <c r="C112" s="12"/>
       <c r="D112" s="13"/>
@@ -4871,7 +5060,9 @@
       <c r="L112" s="2"/>
     </row>
     <row r="113" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A113" s="12"/>
+      <c r="A113" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B113" s="20"/>
       <c r="C113" s="13"/>
       <c r="D113" s="13"/>
@@ -4885,7 +5076,9 @@
       <c r="L113" s="2"/>
     </row>
     <row r="114" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A114" s="12"/>
+      <c r="A114" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B114" s="18"/>
       <c r="C114" s="12"/>
       <c r="D114" s="13"/>
@@ -4899,7 +5092,9 @@
       <c r="L114" s="2"/>
     </row>
     <row r="115" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A115" s="12"/>
+      <c r="A115" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B115" s="16"/>
       <c r="C115" s="13"/>
       <c r="D115" s="13"/>
@@ -4913,7 +5108,9 @@
       <c r="L115" s="2"/>
     </row>
     <row r="116" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A116" s="12"/>
+      <c r="A116" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B116" s="11"/>
       <c r="C116" s="12"/>
       <c r="D116" s="13"/>
@@ -4927,7 +5124,9 @@
       <c r="L116" s="2"/>
     </row>
     <row r="117" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A117" s="12"/>
+      <c r="A117" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B117" s="16"/>
       <c r="C117" s="13"/>
       <c r="D117" s="13"/>
@@ -4941,7 +5140,9 @@
       <c r="L117" s="2"/>
     </row>
     <row r="118" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A118" s="12"/>
+      <c r="A118" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B118" s="11"/>
       <c r="C118" s="12"/>
       <c r="D118" s="13"/>
@@ -4955,7 +5156,9 @@
       <c r="L118" s="2"/>
     </row>
     <row r="119" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A119" s="12"/>
+      <c r="A119" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B119" s="11"/>
       <c r="C119" s="12"/>
       <c r="D119" s="13"/>
@@ -4969,7 +5172,9 @@
       <c r="L119" s="2"/>
     </row>
     <row r="120" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A120" s="12"/>
+      <c r="A120" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B120" s="18"/>
       <c r="C120" s="12"/>
       <c r="D120" s="13"/>
@@ -4983,7 +5188,9 @@
       <c r="L120" s="2"/>
     </row>
     <row r="121" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A121" s="12"/>
+      <c r="A121" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B121" s="16"/>
       <c r="C121" s="13"/>
       <c r="D121" s="13"/>
@@ -4997,7 +5204,9 @@
       <c r="L121" s="2"/>
     </row>
     <row r="122" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A122" s="12"/>
+      <c r="A122" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B122" s="11"/>
       <c r="C122" s="12"/>
       <c r="D122" s="13"/>
@@ -5011,7 +5220,9 @@
       <c r="L122" s="2"/>
     </row>
     <row r="123" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A123" s="12"/>
+      <c r="A123" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B123" s="11"/>
       <c r="C123" s="12"/>
       <c r="D123" s="13"/>
@@ -5025,7 +5236,9 @@
       <c r="L123" s="2"/>
     </row>
     <row r="124" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A124" s="12"/>
+      <c r="A124" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B124" s="18"/>
       <c r="C124" s="12"/>
       <c r="D124" s="13"/>
@@ -5039,7 +5252,9 @@
       <c r="L124" s="2"/>
     </row>
     <row r="125" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A125" s="12"/>
+      <c r="A125" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B125" s="20"/>
       <c r="C125" s="13"/>
       <c r="D125" s="13"/>
@@ -5053,7 +5268,9 @@
       <c r="L125" s="2"/>
     </row>
     <row r="126" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A126" s="12"/>
+      <c r="A126" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B126" s="18"/>
       <c r="C126" s="12"/>
       <c r="D126" s="13"/>
@@ -5067,7 +5284,9 @@
       <c r="L126" s="2"/>
     </row>
     <row r="127" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A127" s="12"/>
+      <c r="A127" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B127" s="16"/>
       <c r="C127" s="13"/>
       <c r="D127" s="13"/>
@@ -5081,7 +5300,9 @@
       <c r="L127" s="2"/>
     </row>
     <row r="128" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A128" s="12"/>
+      <c r="A128" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B128" s="11"/>
       <c r="C128" s="12"/>
       <c r="D128" s="13"/>
@@ -5095,7 +5316,9 @@
       <c r="L128" s="2"/>
     </row>
     <row r="129" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A129" s="12"/>
+      <c r="A129" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B129" s="11"/>
       <c r="C129" s="12"/>
       <c r="D129" s="13"/>
@@ -5109,7 +5332,9 @@
       <c r="L129" s="2"/>
     </row>
     <row r="130" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A130" s="12"/>
+      <c r="A130" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B130" s="18"/>
       <c r="C130" s="12"/>
       <c r="D130" s="13"/>
@@ -5123,7 +5348,9 @@
       <c r="L130" s="2"/>
     </row>
     <row r="131" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A131" s="12"/>
+      <c r="A131" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B131" s="16"/>
       <c r="C131" s="13"/>
       <c r="D131" s="13"/>
@@ -5137,7 +5364,9 @@
       <c r="L131" s="2"/>
     </row>
     <row r="132" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A132" s="12"/>
+      <c r="A132" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B132" s="11"/>
       <c r="C132" s="12"/>
       <c r="D132" s="13"/>
@@ -5151,7 +5380,9 @@
       <c r="L132" s="2"/>
     </row>
     <row r="133" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A133" s="12"/>
+      <c r="A133" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B133" s="11"/>
       <c r="C133" s="12"/>
       <c r="D133" s="13"/>
@@ -5165,7 +5396,9 @@
       <c r="L133" s="2"/>
     </row>
     <row r="134" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A134" s="12"/>
+      <c r="A134" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B134" s="18"/>
       <c r="C134" s="12"/>
       <c r="D134" s="13"/>
@@ -5179,7 +5412,9 @@
       <c r="L134" s="2"/>
     </row>
     <row r="135" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A135" s="12"/>
+      <c r="A135" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B135" s="20"/>
       <c r="C135" s="13"/>
       <c r="D135" s="13"/>
@@ -5193,7 +5428,9 @@
       <c r="L135" s="2"/>
     </row>
     <row r="136" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A136" s="12"/>
+      <c r="A136" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B136" s="18"/>
       <c r="C136" s="12"/>
       <c r="D136" s="13"/>
@@ -5207,7 +5444,9 @@
       <c r="L136" s="2"/>
     </row>
     <row r="137" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A137" s="12"/>
+      <c r="A137" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B137" s="16"/>
       <c r="C137" s="13"/>
       <c r="D137" s="13"/>
@@ -5221,7 +5460,9 @@
       <c r="L137" s="2"/>
     </row>
     <row r="138" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A138" s="12"/>
+      <c r="A138" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B138" s="11"/>
       <c r="C138" s="12"/>
       <c r="D138" s="13"/>
@@ -5235,7 +5476,9 @@
       <c r="L138" s="2"/>
     </row>
     <row r="139" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A139" s="12"/>
+      <c r="A139" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B139" s="11"/>
       <c r="C139" s="12"/>
       <c r="D139" s="13"/>
@@ -5249,7 +5492,9 @@
       <c r="L139" s="2"/>
     </row>
     <row r="140" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A140" s="12"/>
+      <c r="A140" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B140" s="18"/>
       <c r="C140" s="12"/>
       <c r="D140" s="13"/>
@@ -5263,7 +5508,9 @@
       <c r="L140" s="2"/>
     </row>
     <row r="141" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A141" s="12"/>
+      <c r="A141" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B141" s="16"/>
       <c r="C141" s="13"/>
       <c r="D141" s="13"/>
@@ -5277,7 +5524,9 @@
       <c r="L141" s="2"/>
     </row>
     <row r="142" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A142" s="12"/>
+      <c r="A142" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B142" s="11"/>
       <c r="C142" s="12"/>
       <c r="D142" s="13"/>
@@ -5291,7 +5540,9 @@
       <c r="L142" s="2"/>
     </row>
     <row r="143" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A143" s="12"/>
+      <c r="A143" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B143" s="11"/>
       <c r="C143" s="12"/>
       <c r="D143" s="13"/>
@@ -5305,7 +5556,9 @@
       <c r="L143" s="2"/>
     </row>
     <row r="144" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A144" s="12"/>
+      <c r="A144" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B144" s="18"/>
       <c r="C144" s="12"/>
       <c r="D144" s="13"/>
@@ -5319,7 +5572,9 @@
       <c r="L144" s="2"/>
     </row>
     <row r="145" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A145" s="12"/>
+      <c r="A145" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B145" s="20"/>
       <c r="C145" s="13"/>
       <c r="D145" s="13"/>
@@ -5333,7 +5588,9 @@
       <c r="L145" s="2"/>
     </row>
     <row r="146" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A146" s="12"/>
+      <c r="A146" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B146" s="18"/>
       <c r="C146" s="12"/>
       <c r="D146" s="13"/>
@@ -5347,7 +5604,9 @@
       <c r="L146" s="2"/>
     </row>
     <row r="147" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A147" s="12"/>
+      <c r="A147" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B147" s="16"/>
       <c r="C147" s="13"/>
       <c r="D147" s="13"/>
@@ -5361,7 +5620,9 @@
       <c r="L147" s="2"/>
     </row>
     <row r="148" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A148" s="12"/>
+      <c r="A148" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B148" s="11"/>
       <c r="C148" s="12"/>
       <c r="D148" s="13"/>
@@ -5375,7 +5636,9 @@
       <c r="L148" s="2"/>
     </row>
     <row r="149" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A149" s="12"/>
+      <c r="A149" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B149" s="11"/>
       <c r="C149" s="12"/>
       <c r="D149" s="13"/>
@@ -5389,7 +5652,9 @@
       <c r="L149" s="2"/>
     </row>
     <row r="150" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A150" s="12"/>
+      <c r="A150" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B150" s="18"/>
       <c r="C150" s="12"/>
       <c r="D150" s="13"/>
@@ -5403,7 +5668,9 @@
       <c r="L150" s="2"/>
     </row>
     <row r="151" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A151" s="12"/>
+      <c r="A151" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B151" s="16"/>
       <c r="C151" s="13"/>
       <c r="D151" s="13"/>
@@ -5417,7 +5684,9 @@
       <c r="L151" s="2"/>
     </row>
     <row r="152" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A152" s="12"/>
+      <c r="A152" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B152" s="11"/>
       <c r="C152" s="12"/>
       <c r="D152" s="13"/>
@@ -5431,7 +5700,9 @@
       <c r="L152" s="2"/>
     </row>
     <row r="153" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A153" s="12"/>
+      <c r="A153" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B153" s="11"/>
       <c r="C153" s="12"/>
       <c r="D153" s="13"/>
@@ -5445,7 +5716,9 @@
       <c r="L153" s="2"/>
     </row>
     <row r="154" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A154" s="12"/>
+      <c r="A154" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B154" s="18"/>
       <c r="C154" s="12"/>
       <c r="D154" s="13"/>
@@ -5459,7 +5732,9 @@
       <c r="L154" s="2"/>
     </row>
     <row r="155" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A155" s="12"/>
+      <c r="A155" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B155" s="20"/>
       <c r="C155" s="13"/>
       <c r="D155" s="13"/>
@@ -5473,7 +5748,9 @@
       <c r="L155" s="2"/>
     </row>
     <row r="156" spans="1:12" s="15" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A156" s="12"/>
+      <c r="A156" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="B156" s="18"/>
       <c r="C156" s="12"/>
       <c r="D156" s="13"/>
@@ -6089,6 +6366,7 @@
       <c r="L199" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F15" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I260">
     <sortCondition ref="B2"/>
   </sortState>
@@ -6100,8 +6378,8 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="错误" error="请从下拉框选择" sqref="C108:C1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"移动,电信,联通,移动|电信,移动|联通,电信|联通,移动|电信|联通"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="错误" error="请从下拉列表选择" sqref="A2:A156" xr:uid="{000B3C4E-753B-498D-9FBD-3D73C6923B63}">
-      <formula1>"APP,小程序,公众号"</formula1>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="错误" error="请从下拉列表选择" sqref="A2:A156" xr:uid="{C08EEA86-2A27-48D3-AD3D-87D7436BC50D}">
+      <formula1>"短信劫持,小程序,DPI"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
